--- a/neuroscape_collection_checklists.xlsx
+++ b/neuroscape_collection_checklists.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofj-my.sharepoint.com/personal/jakob_barnard_uj_edu/Documents/PARA/3-Resources/TCGs/Neuroscape/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofj-my.sharepoint.com/personal/jakob_barnard_uj_edu/Documents/Documents/GitHub/neuoscapetcg_collecting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1414" documentId="13_ncr:1_{E36B50F8-A2DC-41DB-B9D6-AF0C4A1F79B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{059B93A7-8FEF-4938-914F-F5682AA166B2}"/>
+  <xr:revisionPtr revIDLastSave="1415" documentId="13_ncr:1_{E36B50F8-A2DC-41DB-B9D6-AF0C4A1F79B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE6C4FC4-FD61-436A-AC3F-0E1CA13DEEE4}"/>
   <bookViews>
-    <workbookView xWindow="3050" yWindow="2400" windowWidth="28090" windowHeight="17060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37600" yWindow="2840" windowWidth="28090" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Genesis Collection" sheetId="1" r:id="rId1"/>
@@ -2098,9 +2098,6 @@
     <t>thrasher/cybernetic</t>
   </si>
   <si>
-    <t>Version: 0.8</t>
-  </si>
-  <si>
     <t>Vetted all card numbers, data, info against neurodb, play site, and physical cards where possible.</t>
   </si>
   <si>
@@ -2114,6 +2111,9 @@
   </si>
   <si>
     <t>Fixed formatting to visually break yp by rarity</t>
+  </si>
+  <si>
+    <t>Version: 0.9</t>
   </si>
 </sst>
 </file>
@@ -2875,26 +2875,6 @@
     <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -2916,13 +2896,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2993,7 +2970,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -3042,7 +3019,7 @@
     <xf numFmtId="0" fontId="36" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3062,6 +3039,29 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3403,61 +3403,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="127" t="s">
         <v>621</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
     </row>
     <row r="2" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="80" t="s">
-        <v>690</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
+      <c r="A2" s="127" t="s">
+        <v>695</v>
+      </c>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
     </row>
     <row r="3" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3537,16 +3537,16 @@
       <c r="J5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="129" t="s">
+      <c r="K5" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O5" s="5" t="s">
@@ -3590,7 +3590,7 @@
       <c r="L6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="105" t="b">
+      <c r="M6" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3635,7 +3635,7 @@
       <c r="L7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="105" t="b">
+      <c r="M7" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N7" s="8" t="s">
@@ -3680,7 +3680,7 @@
       <c r="L8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M8" s="107" t="b">
+      <c r="M8" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N8" s="24" t="s">
@@ -3725,7 +3725,7 @@
       <c r="L9" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="107" t="b">
+      <c r="M9" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N9" s="24" t="s">
@@ -3770,7 +3770,7 @@
       <c r="L10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="105" t="b">
+      <c r="M10" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N10" s="8" t="s">
@@ -3815,7 +3815,7 @@
       <c r="L11" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="107" t="b">
+      <c r="M11" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N11" s="24" t="s">
@@ -3860,7 +3860,7 @@
       <c r="L12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="105" t="b">
+      <c r="M12" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N12" s="8" t="s">
@@ -3905,7 +3905,7 @@
       <c r="L13" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M13" s="107" t="b">
+      <c r="M13" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N13" s="24" t="s">
@@ -3950,7 +3950,7 @@
       <c r="L14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M14" s="105" t="b">
+      <c r="M14" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N14" s="8" t="s">
@@ -3995,7 +3995,7 @@
       <c r="L15" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="107" t="b">
+      <c r="M15" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N15" s="24" t="s">
@@ -4031,19 +4031,19 @@
       <c r="I16" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" s="130" t="s">
+      <c r="J16" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O16" s="28"/>
@@ -4079,16 +4079,16 @@
       <c r="J17" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="130" t="s">
+      <c r="K17" s="121" t="s">
         <v>20</v>
       </c>
       <c r="L17" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M17" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N17" s="130" t="s">
+      <c r="M17" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O17" s="28"/>
@@ -4130,7 +4130,7 @@
       <c r="L18" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M18" s="107" t="b">
+      <c r="M18" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N18" s="24" t="s">
@@ -4175,7 +4175,7 @@
       <c r="L19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M19" s="105" t="b">
+      <c r="M19" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N19" s="8" t="s">
@@ -4220,7 +4220,7 @@
       <c r="L20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="105" t="b">
+      <c r="M20" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N20" s="8" t="s">
@@ -4256,19 +4256,19 @@
       <c r="I21" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N21" s="130" t="s">
+      <c r="J21" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O21" s="28"/>
@@ -4310,7 +4310,7 @@
       <c r="L22" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M22" s="107" t="b">
+      <c r="M22" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N22" s="24" t="s">
@@ -4351,16 +4351,16 @@
       <c r="J23" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K23" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" s="129" t="s">
+      <c r="K23" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O23" s="5"/>
@@ -4402,7 +4402,7 @@
       <c r="L24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M24" s="105" t="b">
+      <c r="M24" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N24" s="8" t="s">
@@ -4447,7 +4447,7 @@
       <c r="L25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="105" t="b">
+      <c r="M25" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N25" s="8" t="s">
@@ -4492,7 +4492,7 @@
       <c r="L26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M26" s="105" t="b">
+      <c r="M26" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N26" s="8" t="s">
@@ -4537,7 +4537,7 @@
       <c r="L27" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="105" t="b">
+      <c r="M27" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N27" s="8" t="s">
@@ -4573,19 +4573,19 @@
       <c r="I28" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M28" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N28" s="130" t="s">
+      <c r="J28" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L28" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O28" s="28"/>
@@ -4627,7 +4627,7 @@
       <c r="L29" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M29" s="107" t="b">
+      <c r="M29" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N29" s="24" t="s">
@@ -4672,7 +4672,7 @@
       <c r="L30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M30" s="105" t="b">
+      <c r="M30" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N30" s="8" t="s">
@@ -4717,7 +4717,7 @@
       <c r="L31" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M31" s="107" t="b">
+      <c r="M31" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N31" s="24" t="s">
@@ -4753,19 +4753,19 @@
       <c r="I32" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J32" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N32" s="130" t="s">
+      <c r="J32" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L32" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N32" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O32" s="28"/>
@@ -4807,7 +4807,7 @@
       <c r="L33" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M33" s="107" t="b">
+      <c r="M33" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N33" s="24" t="s">
@@ -4852,7 +4852,7 @@
       <c r="L34" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M34" s="105" t="b">
+      <c r="M34" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N34" s="8" t="s">
@@ -4897,7 +4897,7 @@
       <c r="L35" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M35" s="107" t="b">
+      <c r="M35" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N35" s="24" t="s">
@@ -4942,7 +4942,7 @@
       <c r="L36" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M36" s="107" t="b">
+      <c r="M36" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N36" s="24" t="s">
@@ -4987,7 +4987,7 @@
       <c r="L37" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M37" s="105" t="b">
+      <c r="M37" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N37" s="8" t="s">
@@ -5032,7 +5032,7 @@
       <c r="L38" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="105" t="b">
+      <c r="M38" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N38" s="8" t="s">
@@ -5077,7 +5077,7 @@
       <c r="L39" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="M39" s="110" t="b">
+      <c r="M39" s="101" t="b">
         <v>1</v>
       </c>
       <c r="N39" s="8" t="s">
@@ -5122,7 +5122,7 @@
       <c r="L40" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M40" s="105" t="b">
+      <c r="M40" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N40" s="8" t="s">
@@ -5167,7 +5167,7 @@
       <c r="L41" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M41" s="105" t="b">
+      <c r="M41" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N41" s="8" t="s">
@@ -5212,7 +5212,7 @@
       <c r="L42" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M42" s="105" t="b">
+      <c r="M42" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N42" s="8" t="s">
@@ -5257,7 +5257,7 @@
       <c r="L43" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M43" s="105" t="b">
+      <c r="M43" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N43" s="8" t="s">
@@ -5302,7 +5302,7 @@
       <c r="L44" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M44" s="107" t="b">
+      <c r="M44" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N44" s="24" t="s">
@@ -5338,19 +5338,19 @@
       <c r="I45" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J45" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L45" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M45" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N45" s="130" t="s">
+      <c r="J45" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N45" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O45" s="28"/>
@@ -5383,19 +5383,19 @@
       <c r="I46" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J46" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L46" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N46" s="130" t="s">
+      <c r="J46" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L46" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O46" s="28"/>
@@ -5437,7 +5437,7 @@
       <c r="L47" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M47" s="105" t="b">
+      <c r="M47" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N47" s="8" t="s">
@@ -5482,7 +5482,7 @@
       <c r="L48" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M48" s="107" t="b">
+      <c r="M48" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N48" s="24" t="s">
@@ -5494,7 +5494,7 @@
       <c r="A49" s="25">
         <v>45</v>
       </c>
-      <c r="B49" s="114" t="s">
+      <c r="B49" s="105" t="s">
         <v>123</v>
       </c>
       <c r="C49" s="27" t="s">
@@ -5518,19 +5518,19 @@
       <c r="I49" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J49" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L49" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M49" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N49" s="130" t="s">
+      <c r="J49" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N49" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O49" s="28"/>
@@ -5566,16 +5566,16 @@
       <c r="J50" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K50" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M50" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N50" s="129" t="s">
+      <c r="K50" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N50" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O50" s="5"/>
@@ -5611,16 +5611,16 @@
       <c r="J51" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K51" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M51" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N51" s="129" t="s">
+      <c r="K51" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O51" s="5"/>
@@ -5629,7 +5629,7 @@
       <c r="A52" s="8">
         <v>48</v>
       </c>
-      <c r="B52" s="115" t="s">
+      <c r="B52" s="106" t="s">
         <v>133</v>
       </c>
       <c r="C52" s="10" t="s">
@@ -5662,7 +5662,7 @@
       <c r="L52" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M52" s="105" t="b">
+      <c r="M52" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N52" s="8" t="s">
@@ -5674,7 +5674,7 @@
       <c r="A53" s="14">
         <v>49</v>
       </c>
-      <c r="B53" s="116" t="s">
+      <c r="B53" s="107" t="s">
         <v>135</v>
       </c>
       <c r="C53" s="16" t="s">
@@ -5707,7 +5707,7 @@
       <c r="L53" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M53" s="105" t="b">
+      <c r="M53" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N53" s="8" t="s">
@@ -5734,7 +5734,7 @@
       <c r="F54" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="G54" s="117" t="s">
+      <c r="G54" s="108" t="s">
         <v>651</v>
       </c>
       <c r="H54" s="25">
@@ -5743,19 +5743,19 @@
       <c r="I54" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J54" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M54" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N54" s="130" t="s">
+      <c r="J54" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L54" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O54" s="28"/>
@@ -5764,7 +5764,7 @@
       <c r="A55" s="14">
         <v>51</v>
       </c>
-      <c r="B55" s="116" t="s">
+      <c r="B55" s="107" t="s">
         <v>140</v>
       </c>
       <c r="C55" s="16" t="s">
@@ -5797,7 +5797,7 @@
       <c r="L55" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M55" s="105" t="b">
+      <c r="M55" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N55" s="8" t="s">
@@ -5842,7 +5842,7 @@
       <c r="L56" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M56" s="107" t="b">
+      <c r="M56" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N56" s="24" t="s">
@@ -5854,7 +5854,7 @@
       <c r="A57" s="25">
         <v>53</v>
       </c>
-      <c r="B57" s="114" t="s">
+      <c r="B57" s="105" t="s">
         <v>144</v>
       </c>
       <c r="C57" s="27" t="s">
@@ -5878,19 +5878,19 @@
       <c r="I57" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J57" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M57" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N57" s="130" t="s">
+      <c r="J57" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O57" s="28"/>
@@ -5932,7 +5932,7 @@
       <c r="L58" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M58" s="105" t="b">
+      <c r="M58" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N58" s="8" t="s">
@@ -5971,16 +5971,16 @@
       <c r="J59" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K59" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M59" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N59" s="129" t="s">
+      <c r="K59" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O59" s="5"/>
@@ -6022,7 +6022,7 @@
       <c r="L60" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M60" s="107" t="b">
+      <c r="M60" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N60" s="24" t="s">
@@ -6067,7 +6067,7 @@
       <c r="L61" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M61" s="105" t="b">
+      <c r="M61" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N61" s="8" t="s">
@@ -6112,7 +6112,7 @@
       <c r="L62" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M62" s="107" t="b">
+      <c r="M62" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N62" s="24" t="s">
@@ -6157,7 +6157,7 @@
       <c r="L63" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M63" s="107" t="b">
+      <c r="M63" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N63" s="24" t="s">
@@ -6202,7 +6202,7 @@
       <c r="L64" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M64" s="107" t="b">
+      <c r="M64" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N64" s="24" t="s">
@@ -6247,7 +6247,7 @@
       <c r="L65" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M65" s="107" t="b">
+      <c r="M65" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N65" s="24" t="s">
@@ -6292,7 +6292,7 @@
       <c r="L66" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M66" s="107" t="b">
+      <c r="M66" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N66" s="24" t="s">
@@ -6337,7 +6337,7 @@
       <c r="L67" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M67" s="107" t="b">
+      <c r="M67" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N67" s="24" t="s">
@@ -6349,7 +6349,7 @@
       <c r="A68" s="14">
         <v>64</v>
       </c>
-      <c r="B68" s="116" t="s">
+      <c r="B68" s="107" t="s">
         <v>167</v>
       </c>
       <c r="C68" s="16" t="s">
@@ -6382,7 +6382,7 @@
       <c r="L68" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M68" s="105" t="b">
+      <c r="M68" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N68" s="8" t="s">
@@ -6394,7 +6394,7 @@
       <c r="A69" s="14">
         <v>65</v>
       </c>
-      <c r="B69" s="116" t="s">
+      <c r="B69" s="107" t="s">
         <v>169</v>
       </c>
       <c r="C69" s="16" t="s">
@@ -6427,7 +6427,7 @@
       <c r="L69" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M69" s="105" t="b">
+      <c r="M69" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N69" s="8" t="s">
@@ -6439,7 +6439,7 @@
       <c r="A70" s="8">
         <v>66</v>
       </c>
-      <c r="B70" s="115" t="s">
+      <c r="B70" s="106" t="s">
         <v>171</v>
       </c>
       <c r="C70" s="10" t="s">
@@ -6472,7 +6472,7 @@
       <c r="L70" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M70" s="105" t="b">
+      <c r="M70" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N70" s="8" t="s">
@@ -6484,7 +6484,7 @@
       <c r="A71" s="14">
         <v>67</v>
       </c>
-      <c r="B71" s="116" t="s">
+      <c r="B71" s="107" t="s">
         <v>173</v>
       </c>
       <c r="C71" s="16" t="s">
@@ -6517,7 +6517,7 @@
       <c r="L71" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M71" s="105" t="b">
+      <c r="M71" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N71" s="8" t="s">
@@ -6529,7 +6529,7 @@
       <c r="A72" s="8">
         <v>68</v>
       </c>
-      <c r="B72" s="115" t="s">
+      <c r="B72" s="106" t="s">
         <v>175</v>
       </c>
       <c r="C72" s="10" t="s">
@@ -6562,7 +6562,7 @@
       <c r="L72" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M72" s="105" t="b">
+      <c r="M72" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N72" s="8" t="s">
@@ -6574,7 +6574,7 @@
       <c r="A73" s="14">
         <v>69</v>
       </c>
-      <c r="B73" s="116" t="s">
+      <c r="B73" s="107" t="s">
         <v>177</v>
       </c>
       <c r="C73" s="16" t="s">
@@ -6607,7 +6607,7 @@
       <c r="L73" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M73" s="105" t="b">
+      <c r="M73" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N73" s="8" t="s">
@@ -6652,7 +6652,7 @@
       <c r="L74" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M74" s="105" t="b">
+      <c r="M74" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N74" s="8" t="s">
@@ -6664,7 +6664,7 @@
       <c r="A75" s="14">
         <v>71</v>
       </c>
-      <c r="B75" s="116" t="s">
+      <c r="B75" s="107" t="s">
         <v>183</v>
       </c>
       <c r="C75" s="16" t="s">
@@ -6697,7 +6697,7 @@
       <c r="L75" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M75" s="105" t="b">
+      <c r="M75" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N75" s="8" t="s">
@@ -6709,7 +6709,7 @@
       <c r="A76" s="19">
         <v>72</v>
       </c>
-      <c r="B76" s="120" t="s">
+      <c r="B76" s="111" t="s">
         <v>185</v>
       </c>
       <c r="C76" s="21" t="s">
@@ -6742,7 +6742,7 @@
       <c r="L76" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M76" s="107" t="b">
+      <c r="M76" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N76" s="24" t="s">
@@ -6754,7 +6754,7 @@
       <c r="A77" s="19">
         <v>73</v>
       </c>
-      <c r="B77" s="120" t="s">
+      <c r="B77" s="111" t="s">
         <v>187</v>
       </c>
       <c r="C77" s="21" t="s">
@@ -6787,7 +6787,7 @@
       <c r="L77" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M77" s="107" t="b">
+      <c r="M77" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N77" s="24" t="s">
@@ -6823,19 +6823,19 @@
       <c r="I78" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J78" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K78" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L78" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M78" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N78" s="130" t="s">
+      <c r="J78" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L78" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O78" s="28"/>
@@ -6844,13 +6844,13 @@
       <c r="A79" s="25">
         <v>75</v>
       </c>
-      <c r="B79" s="114" t="s">
+      <c r="B79" s="105" t="s">
         <v>191</v>
       </c>
       <c r="C79" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="D79" s="118" t="s">
+      <c r="D79" s="109" t="s">
         <v>49</v>
       </c>
       <c r="E79" s="25" t="s">
@@ -6868,19 +6868,19 @@
       <c r="I79" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J79" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K79" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L79" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M79" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N79" s="130" t="s">
+      <c r="J79" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L79" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O79" s="28"/>
@@ -6889,7 +6889,7 @@
       <c r="A80" s="19">
         <v>76</v>
       </c>
-      <c r="B80" s="120" t="s">
+      <c r="B80" s="111" t="s">
         <v>193</v>
       </c>
       <c r="C80" s="21" t="s">
@@ -6922,7 +6922,7 @@
       <c r="L80" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M80" s="107" t="b">
+      <c r="M80" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N80" s="24" t="s">
@@ -6949,7 +6949,7 @@
       <c r="F81" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="G81" s="117" t="s">
+      <c r="G81" s="108" t="s">
         <v>648</v>
       </c>
       <c r="H81" s="25">
@@ -6961,16 +6961,16 @@
       <c r="J81" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K81" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L81" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M81" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N81" s="130" t="s">
+      <c r="K81" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O81" s="28"/>
@@ -7006,16 +7006,16 @@
       <c r="J82" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K82" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L82" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M82" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N82" s="130" t="s">
+      <c r="K82" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L82" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N82" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O82" s="28"/>
@@ -7048,19 +7048,19 @@
       <c r="I83" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J83" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K83" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L83" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M83" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N83" s="130" t="s">
+      <c r="J83" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L83" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N83" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O83" s="28"/>
@@ -7096,16 +7096,16 @@
       <c r="J84" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K84" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L84" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M84" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N84" s="129" t="s">
+      <c r="K84" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L84" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N84" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O84" s="5"/>
@@ -7147,7 +7147,7 @@
       <c r="L85" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M85" s="107" t="b">
+      <c r="M85" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N85" s="24" t="s">
@@ -7192,7 +7192,7 @@
       <c r="L86" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M86" s="105" t="b">
+      <c r="M86" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N86" s="8" t="s">
@@ -7231,16 +7231,16 @@
       <c r="J87" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K87" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L87" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M87" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N87" s="129" t="s">
+      <c r="K87" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L87" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N87" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O87" s="5"/>
@@ -7282,7 +7282,7 @@
       <c r="L88" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M88" s="107" t="b">
+      <c r="M88" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N88" s="24" t="s">
@@ -7327,7 +7327,7 @@
       <c r="L89" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M89" s="107" t="b">
+      <c r="M89" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N89" s="24" t="s">
@@ -7372,7 +7372,7 @@
       <c r="L90" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M90" s="107" t="b">
+      <c r="M90" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N90" s="24" t="s">
@@ -7417,7 +7417,7 @@
       <c r="L91" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M91" s="107" t="b">
+      <c r="M91" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N91" s="24" t="s">
@@ -7444,7 +7444,7 @@
       <c r="F92" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="G92" s="119" t="s">
+      <c r="G92" s="110" t="s">
         <v>649</v>
       </c>
       <c r="H92" s="8">
@@ -7462,13 +7462,13 @@
       <c r="L92" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M92" s="105" t="b">
+      <c r="M92" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N92" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="O92" s="119" t="s">
+      <c r="O92" s="110" t="s">
         <v>650</v>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       <c r="L93" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M93" s="105" t="b">
+      <c r="M93" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N93" s="8" t="s">
@@ -7545,19 +7545,19 @@
       <c r="I94" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J94" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K94" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L94" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M94" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N94" s="130" t="s">
+      <c r="J94" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L94" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M94" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N94" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O94" s="28"/>
@@ -7599,7 +7599,7 @@
       <c r="L95" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M95" s="105" t="b">
+      <c r="M95" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N95" s="8" t="s">
@@ -7644,7 +7644,7 @@
       <c r="L96" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M96" s="107" t="b">
+      <c r="M96" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N96" s="24" t="s">
@@ -7689,7 +7689,7 @@
       <c r="L97" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M97" s="107" t="b">
+      <c r="M97" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N97" s="24" t="s">
@@ -7734,7 +7734,7 @@
       <c r="L98" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M98" s="107" t="b">
+      <c r="M98" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N98" s="24" t="s">
@@ -7779,7 +7779,7 @@
       <c r="L99" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M99" s="105" t="b">
+      <c r="M99" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N99" s="8" t="s">
@@ -7824,7 +7824,7 @@
       <c r="L100" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M100" s="107" t="b">
+      <c r="M100" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N100" s="24" t="s">
@@ -7836,7 +7836,7 @@
       <c r="A101" s="8">
         <v>97</v>
       </c>
-      <c r="B101" s="115" t="s">
+      <c r="B101" s="106" t="s">
         <v>240</v>
       </c>
       <c r="C101" s="10" t="s">
@@ -7869,7 +7869,7 @@
       <c r="L101" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M101" s="105" t="b">
+      <c r="M101" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N101" s="8" t="s">
@@ -7881,7 +7881,7 @@
       <c r="A102" s="8">
         <v>98</v>
       </c>
-      <c r="B102" s="115" t="s">
+      <c r="B102" s="106" t="s">
         <v>242</v>
       </c>
       <c r="C102" s="10" t="s">
@@ -7914,7 +7914,7 @@
       <c r="L102" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M102" s="105" t="b">
+      <c r="M102" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N102" s="8" t="s">
@@ -7926,7 +7926,7 @@
       <c r="A103" s="14">
         <v>99</v>
       </c>
-      <c r="B103" s="116" t="s">
+      <c r="B103" s="107" t="s">
         <v>244</v>
       </c>
       <c r="C103" s="16" t="s">
@@ -7959,7 +7959,7 @@
       <c r="L103" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M103" s="105" t="b">
+      <c r="M103" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N103" s="8" t="s">
@@ -8004,7 +8004,7 @@
       <c r="L104" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M104" s="107" t="b">
+      <c r="M104" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N104" s="24" t="s">
@@ -8049,7 +8049,7 @@
       <c r="L105" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M105" s="107" t="b">
+      <c r="M105" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N105" s="24" t="s">
@@ -8061,7 +8061,7 @@
       <c r="A106" s="8">
         <v>102</v>
       </c>
-      <c r="B106" s="115" t="s">
+      <c r="B106" s="106" t="s">
         <v>250</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -8094,7 +8094,7 @@
       <c r="L106" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M106" s="105" t="b">
+      <c r="M106" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N106" s="8" t="s">
@@ -8106,7 +8106,7 @@
       <c r="A107" s="14">
         <v>103</v>
       </c>
-      <c r="B107" s="116" t="s">
+      <c r="B107" s="107" t="s">
         <v>252</v>
       </c>
       <c r="C107" s="16" t="s">
@@ -8139,7 +8139,7 @@
       <c r="L107" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M107" s="105" t="b">
+      <c r="M107" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N107" s="8" t="s">
@@ -8184,7 +8184,7 @@
       <c r="L108" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M108" s="107" t="b">
+      <c r="M108" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N108" s="24" t="s">
@@ -8196,7 +8196,7 @@
       <c r="A109" s="19">
         <v>105</v>
       </c>
-      <c r="B109" s="120" t="s">
+      <c r="B109" s="111" t="s">
         <v>256</v>
       </c>
       <c r="C109" s="21" t="s">
@@ -8229,7 +8229,7 @@
       <c r="L109" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M109" s="107" t="b">
+      <c r="M109" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N109" s="24" t="s">
@@ -8268,16 +8268,16 @@
       <c r="J110" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K110" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L110" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M110" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N110" s="130" t="s">
+      <c r="K110" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L110" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M110" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N110" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O110" s="28"/>
@@ -8286,7 +8286,7 @@
       <c r="A111" s="19">
         <v>107</v>
       </c>
-      <c r="B111" s="120" t="s">
+      <c r="B111" s="111" t="s">
         <v>262</v>
       </c>
       <c r="C111" s="21" t="s">
@@ -8319,7 +8319,7 @@
       <c r="L111" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M111" s="107" t="b">
+      <c r="M111" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N111" s="24" t="s">
@@ -8358,16 +8358,16 @@
       <c r="J112" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K112" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L112" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M112" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N112" s="129" t="s">
+      <c r="K112" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L112" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M112" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N112" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O112" s="5"/>
@@ -8409,7 +8409,7 @@
       <c r="L113" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M113" s="107" t="b">
+      <c r="M113" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N113" s="24" t="s">
@@ -8421,7 +8421,7 @@
       <c r="A114" s="14">
         <v>110</v>
       </c>
-      <c r="B114" s="116" t="s">
+      <c r="B114" s="107" t="s">
         <v>270</v>
       </c>
       <c r="C114" s="16" t="s">
@@ -8454,7 +8454,7 @@
       <c r="L114" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M114" s="105" t="b">
+      <c r="M114" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N114" s="8" t="s">
@@ -8466,7 +8466,7 @@
       <c r="A115" s="8">
         <v>111</v>
       </c>
-      <c r="B115" s="115" t="s">
+      <c r="B115" s="106" t="s">
         <v>272</v>
       </c>
       <c r="C115" s="10" t="s">
@@ -8499,7 +8499,7 @@
       <c r="L115" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M115" s="105" t="b">
+      <c r="M115" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N115" s="8" t="s">
@@ -8511,7 +8511,7 @@
       <c r="A116" s="19">
         <v>112</v>
       </c>
-      <c r="B116" s="120" t="s">
+      <c r="B116" s="111" t="s">
         <v>274</v>
       </c>
       <c r="C116" s="21" t="s">
@@ -8544,7 +8544,7 @@
       <c r="L116" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M116" s="107" t="b">
+      <c r="M116" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N116" s="24" t="s">
@@ -8556,7 +8556,7 @@
       <c r="A117" s="25">
         <v>113</v>
       </c>
-      <c r="B117" s="114" t="s">
+      <c r="B117" s="105" t="s">
         <v>276</v>
       </c>
       <c r="C117" s="27" t="s">
@@ -8580,19 +8580,19 @@
       <c r="I117" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J117" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K117" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L117" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M117" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N117" s="130" t="s">
+      <c r="J117" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K117" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L117" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M117" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N117" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O117" s="28"/>
@@ -8601,7 +8601,7 @@
       <c r="A118" s="25">
         <v>114</v>
       </c>
-      <c r="B118" s="114" t="s">
+      <c r="B118" s="105" t="s">
         <v>278</v>
       </c>
       <c r="C118" s="27" t="s">
@@ -8625,19 +8625,19 @@
       <c r="I118" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J118" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K118" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L118" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M118" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N118" s="130" t="s">
+      <c r="J118" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K118" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L118" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M118" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N118" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O118" s="28"/>
@@ -8646,7 +8646,7 @@
       <c r="A119" s="19">
         <v>115</v>
       </c>
-      <c r="B119" s="120" t="s">
+      <c r="B119" s="111" t="s">
         <v>280</v>
       </c>
       <c r="C119" s="21" t="s">
@@ -8679,7 +8679,7 @@
       <c r="L119" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M119" s="107" t="b">
+      <c r="M119" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N119" s="24" t="s">
@@ -8691,7 +8691,7 @@
       <c r="A120" s="14">
         <v>116</v>
       </c>
-      <c r="B120" s="116" t="s">
+      <c r="B120" s="107" t="s">
         <v>282</v>
       </c>
       <c r="C120" s="16" t="s">
@@ -8724,7 +8724,7 @@
       <c r="L120" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M120" s="105" t="b">
+      <c r="M120" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N120" s="8" t="s">
@@ -8736,7 +8736,7 @@
       <c r="A121" s="19">
         <v>117</v>
       </c>
-      <c r="B121" s="120" t="s">
+      <c r="B121" s="111" t="s">
         <v>284</v>
       </c>
       <c r="C121" s="21" t="s">
@@ -8769,7 +8769,7 @@
       <c r="L121" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M121" s="107" t="b">
+      <c r="M121" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N121" s="24" t="s">
@@ -8781,7 +8781,7 @@
       <c r="A122" s="19">
         <v>118</v>
       </c>
-      <c r="B122" s="120" t="s">
+      <c r="B122" s="111" t="s">
         <v>286</v>
       </c>
       <c r="C122" s="21" t="s">
@@ -8814,7 +8814,7 @@
       <c r="L122" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M122" s="107" t="b">
+      <c r="M122" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N122" s="24" t="s">
@@ -8826,7 +8826,7 @@
       <c r="A123" s="8">
         <v>119</v>
       </c>
-      <c r="B123" s="115" t="s">
+      <c r="B123" s="106" t="s">
         <v>287</v>
       </c>
       <c r="C123" s="10" t="s">
@@ -8859,7 +8859,7 @@
       <c r="L123" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M123" s="105" t="b">
+      <c r="M123" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N123" s="8" t="s">
@@ -8871,7 +8871,7 @@
       <c r="A124" s="8">
         <v>120</v>
       </c>
-      <c r="B124" s="115" t="s">
+      <c r="B124" s="106" t="s">
         <v>289</v>
       </c>
       <c r="C124" s="10" t="s">
@@ -8904,7 +8904,7 @@
       <c r="L124" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M124" s="105" t="b">
+      <c r="M124" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N124" s="8" t="s">
@@ -8949,7 +8949,7 @@
       <c r="L125" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M125" s="107" t="b">
+      <c r="M125" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N125" s="24" t="s">
@@ -8985,19 +8985,19 @@
       <c r="I126" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J126" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K126" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L126" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M126" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N126" s="130" t="s">
+      <c r="J126" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K126" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L126" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M126" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N126" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O126" s="28"/>
@@ -9006,7 +9006,7 @@
       <c r="A127" s="19">
         <v>123</v>
       </c>
-      <c r="B127" s="120" t="s">
+      <c r="B127" s="111" t="s">
         <v>295</v>
       </c>
       <c r="C127" s="21" t="s">
@@ -9039,7 +9039,7 @@
       <c r="L127" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M127" s="107" t="b">
+      <c r="M127" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N127" s="24" t="s">
@@ -9078,16 +9078,16 @@
       <c r="J128" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K128" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L128" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M128" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N128" s="129" t="s">
+      <c r="K128" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L128" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M128" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N128" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O128" s="5"/>
@@ -9129,7 +9129,7 @@
       <c r="L129" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M129" s="107" t="b">
+      <c r="M129" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N129" s="24" t="s">
@@ -9141,7 +9141,7 @@
       <c r="A130" s="14">
         <v>126</v>
       </c>
-      <c r="B130" s="116" t="s">
+      <c r="B130" s="107" t="s">
         <v>301</v>
       </c>
       <c r="C130" s="16" t="s">
@@ -9174,7 +9174,7 @@
       <c r="L130" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M130" s="105" t="b">
+      <c r="M130" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N130" s="8" t="s">
@@ -9219,7 +9219,7 @@
       <c r="L131" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M131" s="107" t="b">
+      <c r="M131" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N131" s="24" t="s">
@@ -9231,7 +9231,7 @@
       <c r="A132" s="14">
         <v>128</v>
       </c>
-      <c r="B132" s="116" t="s">
+      <c r="B132" s="107" t="s">
         <v>305</v>
       </c>
       <c r="C132" s="16" t="s">
@@ -9264,7 +9264,7 @@
       <c r="L132" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M132" s="105" t="b">
+      <c r="M132" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N132" s="8" t="s">
@@ -9309,7 +9309,7 @@
       <c r="L133" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M133" s="105" t="b">
+      <c r="M133" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N133" s="8" t="s">
@@ -9354,7 +9354,7 @@
       <c r="L134" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M134" s="107" t="b">
+      <c r="M134" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N134" s="24" t="s">
@@ -9366,7 +9366,7 @@
       <c r="A135" s="14">
         <v>131</v>
       </c>
-      <c r="B135" s="116" t="s">
+      <c r="B135" s="107" t="s">
         <v>311</v>
       </c>
       <c r="C135" s="16" t="s">
@@ -9399,7 +9399,7 @@
       <c r="L135" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M135" s="105" t="b">
+      <c r="M135" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N135" s="8" t="s">
@@ -9411,7 +9411,7 @@
       <c r="A136" s="19">
         <v>132</v>
       </c>
-      <c r="B136" s="120" t="s">
+      <c r="B136" s="111" t="s">
         <v>313</v>
       </c>
       <c r="C136" s="21" t="s">
@@ -9444,7 +9444,7 @@
       <c r="L136" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M136" s="107" t="b">
+      <c r="M136" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N136" s="24" t="s">
@@ -9489,7 +9489,7 @@
       <c r="L137" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M137" s="107" t="b">
+      <c r="M137" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N137" s="24" t="s">
@@ -9501,7 +9501,7 @@
       <c r="A138" s="19">
         <v>134</v>
       </c>
-      <c r="B138" s="120" t="s">
+      <c r="B138" s="111" t="s">
         <v>318</v>
       </c>
       <c r="C138" s="21" t="s">
@@ -9534,7 +9534,7 @@
       <c r="L138" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M138" s="107" t="b">
+      <c r="M138" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N138" s="24" t="s">
@@ -9573,16 +9573,16 @@
       <c r="J139" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K139" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L139" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M139" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N139" s="130" t="s">
+      <c r="K139" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L139" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M139" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N139" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O139" s="28"/>
@@ -9624,7 +9624,7 @@
       <c r="L140" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M140" s="107" t="b">
+      <c r="M140" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N140" s="24" t="s">
@@ -9660,19 +9660,19 @@
       <c r="I141" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J141" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K141" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L141" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M141" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N141" s="130" t="s">
+      <c r="J141" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K141" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L141" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M141" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N141" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O141" s="28"/>
@@ -9714,7 +9714,7 @@
       <c r="L142" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M142" s="107" t="b">
+      <c r="M142" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N142" s="24" t="s">
@@ -9753,16 +9753,16 @@
       <c r="J143" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K143" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L143" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M143" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N143" s="129" t="s">
+      <c r="K143" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L143" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M143" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N143" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O143" s="5"/>
@@ -9798,16 +9798,16 @@
       <c r="J144" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K144" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L144" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M144" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N144" s="129" t="s">
+      <c r="K144" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L144" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M144" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N144" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O144" s="5"/>
@@ -9816,7 +9816,7 @@
       <c r="A145" s="19">
         <v>141</v>
       </c>
-      <c r="B145" s="120" t="s">
+      <c r="B145" s="111" t="s">
         <v>334</v>
       </c>
       <c r="C145" s="21" t="s">
@@ -9849,7 +9849,7 @@
       <c r="L145" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M145" s="107" t="b">
+      <c r="M145" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N145" s="24" t="s">
@@ -9894,7 +9894,7 @@
       <c r="L146" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M146" s="105" t="b">
+      <c r="M146" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N146" s="8" t="s">
@@ -9939,7 +9939,7 @@
       <c r="L147" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M147" s="105" t="b">
+      <c r="M147" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N147" s="8" t="s">
@@ -9978,16 +9978,16 @@
       <c r="J148" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K148" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L148" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M148" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N148" s="129" t="s">
+      <c r="K148" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L148" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M148" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N148" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O148" s="5"/>
@@ -10029,7 +10029,7 @@
       <c r="L149" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M149" s="105" t="b">
+      <c r="M149" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N149" s="8" t="s">
@@ -10074,7 +10074,7 @@
       <c r="L150" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M150" s="107" t="b">
+      <c r="M150" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N150" s="24" t="s">
@@ -10113,16 +10113,16 @@
       <c r="J151" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K151" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L151" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M151" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N151" s="130" t="s">
+      <c r="K151" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L151" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M151" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N151" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O151" s="28"/>
@@ -10164,7 +10164,7 @@
       <c r="L152" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M152" s="107" t="b">
+      <c r="M152" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N152" s="24" t="s">
@@ -10209,7 +10209,7 @@
       <c r="L153" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M153" s="107" t="b">
+      <c r="M153" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N153" s="24" t="s">
@@ -10254,7 +10254,7 @@
       <c r="L154" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M154" s="105" t="b">
+      <c r="M154" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N154" s="8" t="s">
@@ -10299,7 +10299,7 @@
       <c r="L155" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M155" s="107" t="b">
+      <c r="M155" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N155" s="24" t="s">
@@ -10335,19 +10335,19 @@
       <c r="I156" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J156" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="K156" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L156" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M156" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N156" s="130" t="s">
+      <c r="J156" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="K156" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L156" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M156" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N156" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O156" s="28"/>
@@ -10389,7 +10389,7 @@
       <c r="L157" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M157" s="105" t="b">
+      <c r="M157" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N157" s="8" t="s">
@@ -10434,7 +10434,7 @@
       <c r="L158" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M158" s="105" t="b">
+      <c r="M158" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N158" s="8" t="s">
@@ -10479,7 +10479,7 @@
       <c r="L159" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M159" s="107" t="b">
+      <c r="M159" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N159" s="24" t="s">
@@ -10524,7 +10524,7 @@
       <c r="L160" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M160" s="105" t="b">
+      <c r="M160" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N160" s="8" t="s">
@@ -10569,7 +10569,7 @@
       <c r="L161" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M161" s="107" t="b">
+      <c r="M161" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N161" s="24" t="s">
@@ -10614,7 +10614,7 @@
       <c r="L162" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M162" s="105" t="b">
+      <c r="M162" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N162" s="8" t="s">
@@ -10659,7 +10659,7 @@
       <c r="L163" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M163" s="105" t="b">
+      <c r="M163" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N163" s="8" t="s">
@@ -10704,7 +10704,7 @@
       <c r="L164" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M164" s="107" t="b">
+      <c r="M164" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N164" s="24" t="s">
@@ -10743,16 +10743,16 @@
       <c r="J165" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K165" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L165" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M165" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N165" s="130" t="s">
+      <c r="K165" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L165" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M165" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N165" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O165" s="28"/>
@@ -10794,7 +10794,7 @@
       <c r="L166" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M166" s="105" t="b">
+      <c r="M166" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N166" s="8" t="s">
@@ -10839,7 +10839,7 @@
       <c r="L167" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M167" s="105" t="b">
+      <c r="M167" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N167" s="8" t="s">
@@ -10884,7 +10884,7 @@
       <c r="L168" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M168" s="107" t="b">
+      <c r="M168" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N168" s="24" t="s">
@@ -10929,7 +10929,7 @@
       <c r="L169" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M169" s="105" t="b">
+      <c r="M169" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N169" s="8" t="s">
@@ -10974,7 +10974,7 @@
       <c r="L170" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M170" s="107" t="b">
+      <c r="M170" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N170" s="24" t="s">
@@ -11019,7 +11019,7 @@
       <c r="L171" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M171" s="107" t="b">
+      <c r="M171" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N171" s="24" t="s">
@@ -11064,7 +11064,7 @@
       <c r="L172" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M172" s="107" t="b">
+      <c r="M172" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N172" s="24" t="s">
@@ -11100,19 +11100,19 @@
       <c r="I173" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J173" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K173" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L173" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M173" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N173" s="130" t="s">
+      <c r="J173" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K173" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L173" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M173" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N173" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O173" s="28"/>
@@ -11145,19 +11145,19 @@
       <c r="I174" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J174" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K174" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L174" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M174" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N174" s="130" t="s">
+      <c r="J174" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K174" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L174" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M174" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N174" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O174" s="28"/>
@@ -11166,7 +11166,7 @@
       <c r="A175" s="14">
         <v>171</v>
       </c>
-      <c r="B175" s="116" t="s">
+      <c r="B175" s="107" t="s">
         <v>398</v>
       </c>
       <c r="C175" s="16" t="s">
@@ -11199,7 +11199,7 @@
       <c r="L175" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M175" s="105" t="b">
+      <c r="M175" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N175" s="8" t="s">
@@ -11244,7 +11244,7 @@
       <c r="L176" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M176" s="107" t="b">
+      <c r="M176" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N176" s="24" t="s">
@@ -11256,7 +11256,7 @@
       <c r="A177" s="14">
         <v>173</v>
       </c>
-      <c r="B177" s="116" t="s">
+      <c r="B177" s="107" t="s">
         <v>403</v>
       </c>
       <c r="C177" s="16" t="s">
@@ -11289,7 +11289,7 @@
       <c r="L177" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M177" s="105" t="b">
+      <c r="M177" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N177" s="8" t="s">
@@ -11334,7 +11334,7 @@
       <c r="L178" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M178" s="107" t="b">
+      <c r="M178" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N178" s="24" t="s">
@@ -11379,7 +11379,7 @@
       <c r="L179" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M179" s="107" t="b">
+      <c r="M179" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N179" s="24" t="s">
@@ -11424,7 +11424,7 @@
       <c r="L180" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M180" s="107" t="b">
+      <c r="M180" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N180" s="24" t="s">
@@ -11460,19 +11460,19 @@
       <c r="I181" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J181" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K181" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L181" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M181" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N181" s="130" t="s">
+      <c r="J181" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K181" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L181" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M181" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N181" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O181" s="28"/>
@@ -11481,7 +11481,7 @@
       <c r="A182" s="8">
         <v>178</v>
       </c>
-      <c r="B182" s="115" t="s">
+      <c r="B182" s="106" t="s">
         <v>414</v>
       </c>
       <c r="C182" s="10" t="s">
@@ -11514,7 +11514,7 @@
       <c r="L182" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M182" s="105" t="b">
+      <c r="M182" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N182" s="8" t="s">
@@ -11526,7 +11526,7 @@
       <c r="A183" s="14">
         <v>179</v>
       </c>
-      <c r="B183" s="116" t="s">
+      <c r="B183" s="107" t="s">
         <v>416</v>
       </c>
       <c r="C183" s="16" t="s">
@@ -11559,7 +11559,7 @@
       <c r="L183" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M183" s="105" t="b">
+      <c r="M183" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N183" s="8" t="s">
@@ -11604,7 +11604,7 @@
       <c r="L184" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M184" s="107" t="b">
+      <c r="M184" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N184" s="24" t="s">
@@ -11640,19 +11640,19 @@
       <c r="I185" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J185" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K185" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L185" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M185" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N185" s="130" t="s">
+      <c r="J185" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K185" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L185" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M185" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N185" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O185" s="28"/>
@@ -11685,19 +11685,19 @@
       <c r="I186" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J186" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K186" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L186" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M186" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N186" s="130" t="s">
+      <c r="J186" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K186" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L186" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M186" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N186" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O186" s="28"/>
@@ -11733,16 +11733,16 @@
       <c r="J187" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K187" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L187" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M187" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N187" s="129" t="s">
+      <c r="K187" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L187" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M187" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N187" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O187" s="5"/>
@@ -11778,16 +11778,16 @@
       <c r="J188" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K188" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L188" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M188" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N188" s="129" t="s">
+      <c r="K188" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L188" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M188" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N188" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O188" s="5"/>
@@ -11820,19 +11820,19 @@
       <c r="I189" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J189" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K189" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L189" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M189" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N189" s="130" t="s">
+      <c r="J189" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K189" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L189" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M189" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N189" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O189" s="28"/>
@@ -11874,7 +11874,7 @@
       <c r="L190" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M190" s="105" t="b">
+      <c r="M190" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N190" s="8" t="s">
@@ -11919,7 +11919,7 @@
       <c r="L191" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M191" s="105" t="b">
+      <c r="M191" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N191" s="8" t="s">
@@ -11964,7 +11964,7 @@
       <c r="L192" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M192" s="105" t="b">
+      <c r="M192" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N192" s="8" t="s">
@@ -12003,16 +12003,16 @@
       <c r="J193" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K193" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L193" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M193" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N193" s="129" t="s">
+      <c r="K193" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L193" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M193" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N193" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O193" s="5"/>
@@ -12021,7 +12021,7 @@
       <c r="A194" s="19">
         <v>190</v>
       </c>
-      <c r="B194" s="120" t="s">
+      <c r="B194" s="111" t="s">
         <v>439</v>
       </c>
       <c r="C194" s="21" t="s">
@@ -12054,7 +12054,7 @@
       <c r="L194" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M194" s="107" t="b">
+      <c r="M194" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N194" s="24" t="s">
@@ -12099,7 +12099,7 @@
       <c r="L195" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M195" s="107" t="b">
+      <c r="M195" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N195" s="24" t="s">
@@ -12111,7 +12111,7 @@
       <c r="A196" s="19">
         <v>192</v>
       </c>
-      <c r="B196" s="120" t="s">
+      <c r="B196" s="111" t="s">
         <v>442</v>
       </c>
       <c r="C196" s="21" t="s">
@@ -12144,7 +12144,7 @@
       <c r="L196" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M196" s="107" t="b">
+      <c r="M196" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N196" s="24" t="s">
@@ -12156,7 +12156,7 @@
       <c r="A197" s="19">
         <v>193</v>
       </c>
-      <c r="B197" s="120" t="s">
+      <c r="B197" s="111" t="s">
         <v>444</v>
       </c>
       <c r="C197" s="21" t="s">
@@ -12189,7 +12189,7 @@
       <c r="L197" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M197" s="107" t="b">
+      <c r="M197" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N197" s="24" t="s">
@@ -12201,7 +12201,7 @@
       <c r="A198" s="25">
         <v>194</v>
       </c>
-      <c r="B198" s="114" t="s">
+      <c r="B198" s="105" t="s">
         <v>446</v>
       </c>
       <c r="C198" s="27" t="s">
@@ -12225,19 +12225,19 @@
       <c r="I198" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J198" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K198" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L198" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M198" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N198" s="130" t="s">
+      <c r="J198" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K198" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L198" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M198" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N198" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O198" s="28"/>
@@ -12270,19 +12270,19 @@
       <c r="I199" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J199" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K199" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L199" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M199" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N199" s="130" t="s">
+      <c r="J199" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K199" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L199" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M199" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N199" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O199" s="28"/>
@@ -12324,7 +12324,7 @@
       <c r="L200" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M200" s="107" t="b">
+      <c r="M200" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N200" s="24" t="s">
@@ -12369,7 +12369,7 @@
       <c r="L201" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M201" s="107" t="b">
+      <c r="M201" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N201" s="24" t="s">
@@ -12405,19 +12405,19 @@
       <c r="I202" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J202" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K202" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="L202" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="M202" s="108" t="b">
-        <v>1</v>
-      </c>
-      <c r="N202" s="130" t="s">
+      <c r="J202" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K202" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="L202" s="122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M202" s="99" t="b">
+        <v>1</v>
+      </c>
+      <c r="N202" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O202" s="28"/>
@@ -12459,7 +12459,7 @@
       <c r="L203" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M203" s="107" t="b">
+      <c r="M203" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N203" s="24" t="s">
@@ -12471,7 +12471,7 @@
       <c r="A204" s="8">
         <v>200</v>
       </c>
-      <c r="B204" s="115" t="s">
+      <c r="B204" s="106" t="s">
         <v>458</v>
       </c>
       <c r="C204" s="10" t="s">
@@ -12504,13 +12504,13 @@
       <c r="L204" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M204" s="105" t="b">
+      <c r="M204" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N204" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="O204" s="119" t="s">
+      <c r="O204" s="110" t="s">
         <v>652</v>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
       <c r="A205" s="14">
         <v>201</v>
       </c>
-      <c r="B205" s="116" t="s">
+      <c r="B205" s="107" t="s">
         <v>461</v>
       </c>
       <c r="C205" s="16" t="s">
@@ -12551,7 +12551,7 @@
       <c r="L205" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M205" s="105" t="b">
+      <c r="M205" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N205" s="8" t="s">
@@ -12565,7 +12565,7 @@
       <c r="A206" s="8">
         <v>202</v>
       </c>
-      <c r="B206" s="115" t="s">
+      <c r="B206" s="106" t="s">
         <v>463</v>
       </c>
       <c r="C206" s="10" t="s">
@@ -12598,13 +12598,13 @@
       <c r="L206" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M206" s="105" t="b">
+      <c r="M206" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N206" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="O206" s="119" t="s">
+      <c r="O206" s="110" t="s">
         <v>652</v>
       </c>
     </row>
@@ -12642,16 +12642,16 @@
       <c r="K207" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L207" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M207" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N207" s="129" t="s">
-        <v>616</v>
-      </c>
-      <c r="O207" s="121" t="s">
+      <c r="L207" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M207" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N207" s="120" t="s">
+        <v>616</v>
+      </c>
+      <c r="O207" s="112" t="s">
         <v>652</v>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       <c r="L208" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M208" s="107" t="b">
+      <c r="M208" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N208" s="24" t="s">
@@ -12730,19 +12730,19 @@
       <c r="I209" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J209" s="130" t="s">
+      <c r="J209" s="121" t="s">
         <v>20</v>
       </c>
       <c r="K209" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="L209" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M209" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N209" s="130" t="s">
+      <c r="L209" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M209" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N209" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O209" s="28" t="s">
@@ -12780,25 +12780,25 @@
       <c r="J210" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K210" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L210" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M210" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N210" s="129" t="s">
-        <v>616</v>
-      </c>
-      <c r="O210" s="121"/>
+      <c r="K210" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L210" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M210" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N210" s="120" t="s">
+        <v>616</v>
+      </c>
+      <c r="O210" s="112"/>
     </row>
     <row r="211" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>207</v>
       </c>
-      <c r="B211" s="122" t="s">
+      <c r="B211" s="113" t="s">
         <v>475</v>
       </c>
       <c r="C211" s="4" t="s">
@@ -12825,19 +12825,19 @@
       <c r="J211" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K211" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L211" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M211" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N211" s="129" t="s">
-        <v>616</v>
-      </c>
-      <c r="O211" s="121"/>
+      <c r="K211" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L211" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M211" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N211" s="120" t="s">
+        <v>616</v>
+      </c>
+      <c r="O211" s="112"/>
     </row>
     <row r="212" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="19">
@@ -12876,7 +12876,7 @@
       <c r="L212" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M212" s="107" t="b">
+      <c r="M212" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N212" s="24" t="s">
@@ -12921,7 +12921,7 @@
       <c r="L213" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M213" s="107" t="b">
+      <c r="M213" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N213" s="24" t="s">
@@ -12957,19 +12957,19 @@
       <c r="I214" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J214" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K214" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L214" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M214" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N214" s="130" t="s">
+      <c r="J214" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K214" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L214" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M214" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N214" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O214" s="28"/>
@@ -13011,7 +13011,7 @@
       <c r="L215" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M215" s="105" t="b">
+      <c r="M215" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N215" s="8" t="s">
@@ -13047,19 +13047,19 @@
       <c r="I216" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J216" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K216" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L216" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M216" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N216" s="130" t="s">
+      <c r="J216" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K216" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L216" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M216" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N216" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O216" s="28"/>
@@ -13068,7 +13068,7 @@
       <c r="A217" s="19">
         <v>213</v>
       </c>
-      <c r="B217" s="120" t="s">
+      <c r="B217" s="111" t="s">
         <v>486</v>
       </c>
       <c r="C217" s="21" t="s">
@@ -13101,7 +13101,7 @@
       <c r="L217" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M217" s="107" t="b">
+      <c r="M217" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N217" s="24" t="s">
@@ -13113,7 +13113,7 @@
       <c r="A218" s="8">
         <v>214</v>
       </c>
-      <c r="B218" s="115" t="s">
+      <c r="B218" s="106" t="s">
         <v>488</v>
       </c>
       <c r="C218" s="10" t="s">
@@ -13146,7 +13146,7 @@
       <c r="L218" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M218" s="105" t="b">
+      <c r="M218" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N218" s="8" t="s">
@@ -13158,7 +13158,7 @@
       <c r="A219" s="14">
         <v>215</v>
       </c>
-      <c r="B219" s="116" t="s">
+      <c r="B219" s="107" t="s">
         <v>490</v>
       </c>
       <c r="C219" s="16" t="s">
@@ -13191,7 +13191,7 @@
       <c r="L219" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M219" s="105" t="b">
+      <c r="M219" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N219" s="8" t="s">
@@ -13236,7 +13236,7 @@
       <c r="L220" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M220" s="107" t="b">
+      <c r="M220" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N220" s="24" t="s">
@@ -13248,7 +13248,7 @@
       <c r="A221" s="25">
         <v>217</v>
       </c>
-      <c r="B221" s="114" t="s">
+      <c r="B221" s="105" t="s">
         <v>494</v>
       </c>
       <c r="C221" s="27" t="s">
@@ -13263,7 +13263,7 @@
       <c r="F221" s="28" t="s">
         <v>500</v>
       </c>
-      <c r="G221" s="117" t="s">
+      <c r="G221" s="108" t="s">
         <v>645</v>
       </c>
       <c r="H221" s="25">
@@ -13272,19 +13272,19 @@
       <c r="I221" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J221" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K221" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L221" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M221" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N221" s="130" t="s">
+      <c r="J221" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K221" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L221" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M221" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N221" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O221" s="28"/>
@@ -13326,7 +13326,7 @@
       <c r="L222" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M222" s="105" t="b">
+      <c r="M222" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N222" s="8" t="s">
@@ -13365,16 +13365,16 @@
       <c r="J223" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K223" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L223" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M223" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N223" s="129" t="s">
+      <c r="K223" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L223" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M223" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N223" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O223" s="5"/>
@@ -13410,16 +13410,16 @@
       <c r="J224" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K224" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L224" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M224" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N224" s="129" t="s">
+      <c r="K224" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L224" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M224" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N224" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O224" s="5"/>
@@ -13461,7 +13461,7 @@
       <c r="L225" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M225" s="105" t="b">
+      <c r="M225" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N225" s="8" t="s">
@@ -13488,7 +13488,7 @@
       <c r="F226" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G226" s="121" t="s">
+      <c r="G226" s="112" t="s">
         <v>653</v>
       </c>
       <c r="H226" s="2">
@@ -13500,16 +13500,16 @@
       <c r="J226" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K226" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L226" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M226" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N226" s="129" t="s">
+      <c r="K226" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L226" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M226" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N226" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O226" s="5"/>
@@ -13518,7 +13518,7 @@
       <c r="A227" s="25">
         <v>223</v>
       </c>
-      <c r="B227" s="114" t="s">
+      <c r="B227" s="105" t="s">
         <v>510</v>
       </c>
       <c r="C227" s="27" t="s">
@@ -13533,7 +13533,7 @@
       <c r="F227" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="G227" s="117" t="s">
+      <c r="G227" s="108" t="s">
         <v>653</v>
       </c>
       <c r="H227" s="25">
@@ -13542,19 +13542,19 @@
       <c r="I227" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J227" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K227" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L227" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M227" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N227" s="130" t="s">
+      <c r="J227" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K227" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L227" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M227" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N227" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O227" s="28"/>
@@ -13563,7 +13563,7 @@
       <c r="A228" s="8">
         <v>224</v>
       </c>
-      <c r="B228" s="115" t="s">
+      <c r="B228" s="106" t="s">
         <v>513</v>
       </c>
       <c r="C228" s="10" t="s">
@@ -13578,7 +13578,7 @@
       <c r="F228" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G228" s="119" t="s">
+      <c r="G228" s="110" t="s">
         <v>653</v>
       </c>
       <c r="H228" s="8">
@@ -13596,7 +13596,7 @@
       <c r="L228" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M228" s="105" t="b">
+      <c r="M228" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N228" s="8" t="s">
@@ -13608,7 +13608,7 @@
       <c r="A229" s="8">
         <v>225</v>
       </c>
-      <c r="B229" s="115" t="s">
+      <c r="B229" s="106" t="s">
         <v>515</v>
       </c>
       <c r="C229" s="10" t="s">
@@ -13623,7 +13623,7 @@
       <c r="F229" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G229" s="119" t="s">
+      <c r="G229" s="110" t="s">
         <v>653</v>
       </c>
       <c r="H229" s="8">
@@ -13641,7 +13641,7 @@
       <c r="L229" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M229" s="105" t="b">
+      <c r="M229" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N229" s="8" t="s">
@@ -13653,7 +13653,7 @@
       <c r="A230" s="8">
         <v>226</v>
       </c>
-      <c r="B230" s="115" t="s">
+      <c r="B230" s="106" t="s">
         <v>517</v>
       </c>
       <c r="C230" s="10" t="s">
@@ -13668,7 +13668,7 @@
       <c r="F230" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G230" s="119" t="s">
+      <c r="G230" s="110" t="s">
         <v>653</v>
       </c>
       <c r="H230" s="8">
@@ -13686,7 +13686,7 @@
       <c r="L230" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M230" s="105" t="b">
+      <c r="M230" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N230" s="8" t="s">
@@ -13698,7 +13698,7 @@
       <c r="A231" s="25">
         <v>227</v>
       </c>
-      <c r="B231" s="114" t="s">
+      <c r="B231" s="105" t="s">
         <v>519</v>
       </c>
       <c r="C231" s="27" t="s">
@@ -13713,7 +13713,7 @@
       <c r="F231" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="G231" s="123" t="s">
+      <c r="G231" s="114" t="s">
         <v>653</v>
       </c>
       <c r="H231" s="25">
@@ -13722,19 +13722,19 @@
       <c r="I231" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J231" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K231" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L231" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M231" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N231" s="130" t="s">
+      <c r="J231" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K231" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L231" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M231" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N231" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O231" s="28"/>
@@ -13776,7 +13776,7 @@
       <c r="L232" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M232" s="107" t="b">
+      <c r="M232" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N232" s="24" t="s">
@@ -13788,7 +13788,7 @@
       <c r="A233" s="8">
         <v>229</v>
       </c>
-      <c r="B233" s="115" t="s">
+      <c r="B233" s="106" t="s">
         <v>523</v>
       </c>
       <c r="C233" s="10" t="s">
@@ -13803,7 +13803,7 @@
       <c r="F233" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G233" s="119" t="s">
+      <c r="G233" s="110" t="s">
         <v>653</v>
       </c>
       <c r="H233" s="8">
@@ -13821,7 +13821,7 @@
       <c r="L233" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M233" s="105" t="b">
+      <c r="M233" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N233" s="8" t="s">
@@ -13866,7 +13866,7 @@
       <c r="L234" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M234" s="107" t="b">
+      <c r="M234" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N234" s="24" t="s">
@@ -13911,7 +13911,7 @@
       <c r="L235" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M235" s="107" t="b">
+      <c r="M235" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N235" s="24" t="s">
@@ -13947,19 +13947,19 @@
       <c r="I236" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J236" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="K236" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L236" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M236" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N236" s="130" t="s">
+      <c r="J236" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="K236" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L236" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M236" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N236" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O236" s="28"/>
@@ -13983,7 +13983,7 @@
       <c r="F237" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G237" s="121" t="s">
+      <c r="G237" s="112" t="s">
         <v>653</v>
       </c>
       <c r="H237" s="2">
@@ -13995,16 +13995,16 @@
       <c r="J237" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K237" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L237" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M237" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N237" s="129" t="s">
+      <c r="K237" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L237" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M237" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N237" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O237" s="5"/>
@@ -14046,7 +14046,7 @@
       <c r="L238" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M238" s="107" t="b">
+      <c r="M238" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N238" s="24" t="s">
@@ -14058,7 +14058,7 @@
       <c r="A239" s="8">
         <v>235</v>
       </c>
-      <c r="B239" s="115" t="s">
+      <c r="B239" s="106" t="s">
         <v>536</v>
       </c>
       <c r="C239" s="10" t="s">
@@ -14091,7 +14091,7 @@
       <c r="L239" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M239" s="105" t="b">
+      <c r="M239" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N239" s="8" t="s">
@@ -14103,7 +14103,7 @@
       <c r="A240" s="8">
         <v>236</v>
       </c>
-      <c r="B240" s="115" t="s">
+      <c r="B240" s="106" t="s">
         <v>538</v>
       </c>
       <c r="C240" s="10" t="s">
@@ -14136,7 +14136,7 @@
       <c r="L240" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M240" s="105" t="b">
+      <c r="M240" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N240" s="8" t="s">
@@ -14148,7 +14148,7 @@
       <c r="A241" s="8">
         <v>237</v>
       </c>
-      <c r="B241" s="115" t="s">
+      <c r="B241" s="106" t="s">
         <v>539</v>
       </c>
       <c r="C241" s="10" t="s">
@@ -14181,7 +14181,7 @@
       <c r="L241" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M241" s="105" t="b">
+      <c r="M241" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N241" s="8" t="s">
@@ -14193,7 +14193,7 @@
       <c r="A242" s="8">
         <v>238</v>
       </c>
-      <c r="B242" s="115" t="s">
+      <c r="B242" s="106" t="s">
         <v>540</v>
       </c>
       <c r="C242" s="10" t="s">
@@ -14226,7 +14226,7 @@
       <c r="L242" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M242" s="105" t="b">
+      <c r="M242" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N242" s="8" t="s">
@@ -14238,7 +14238,7 @@
       <c r="A243" s="8">
         <v>239</v>
       </c>
-      <c r="B243" s="115" t="s">
+      <c r="B243" s="106" t="s">
         <v>541</v>
       </c>
       <c r="C243" s="10" t="s">
@@ -14271,7 +14271,7 @@
       <c r="L243" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M243" s="105" t="b">
+      <c r="M243" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N243" s="8" t="s">
@@ -14283,7 +14283,7 @@
       <c r="A244" s="8">
         <v>240</v>
       </c>
-      <c r="B244" s="115" t="s">
+      <c r="B244" s="106" t="s">
         <v>543</v>
       </c>
       <c r="C244" s="10" t="s">
@@ -14316,7 +14316,7 @@
       <c r="L244" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M244" s="105" t="b">
+      <c r="M244" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N244" s="8" t="s">
@@ -14328,7 +14328,7 @@
       <c r="A245" s="8">
         <v>241</v>
       </c>
-      <c r="B245" s="115" t="s">
+      <c r="B245" s="106" t="s">
         <v>545</v>
       </c>
       <c r="C245" s="10" t="s">
@@ -14361,7 +14361,7 @@
       <c r="L245" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M245" s="105" t="b">
+      <c r="M245" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N245" s="8" t="s">
@@ -14373,7 +14373,7 @@
       <c r="A246" s="8">
         <v>242</v>
       </c>
-      <c r="B246" s="115" t="s">
+      <c r="B246" s="106" t="s">
         <v>549</v>
       </c>
       <c r="C246" s="10" t="s">
@@ -14406,7 +14406,7 @@
       <c r="L246" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M246" s="105" t="b">
+      <c r="M246" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N246" s="8" t="s">
@@ -14418,7 +14418,7 @@
       <c r="A247" s="8">
         <v>243</v>
       </c>
-      <c r="B247" s="115" t="s">
+      <c r="B247" s="106" t="s">
         <v>551</v>
       </c>
       <c r="C247" s="10" t="s">
@@ -14451,7 +14451,7 @@
       <c r="L247" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M247" s="105" t="b">
+      <c r="M247" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N247" s="8" t="s">
@@ -14463,7 +14463,7 @@
       <c r="A248" s="8">
         <v>244</v>
       </c>
-      <c r="B248" s="115" t="s">
+      <c r="B248" s="106" t="s">
         <v>553</v>
       </c>
       <c r="C248" s="10" t="s">
@@ -14496,7 +14496,7 @@
       <c r="L248" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M248" s="105" t="b">
+      <c r="M248" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N248" s="8" t="s">
@@ -14508,7 +14508,7 @@
       <c r="A249" s="8">
         <v>245</v>
       </c>
-      <c r="B249" s="115" t="s">
+      <c r="B249" s="106" t="s">
         <v>555</v>
       </c>
       <c r="C249" s="10" t="s">
@@ -14541,7 +14541,7 @@
       <c r="L249" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M249" s="105" t="b">
+      <c r="M249" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N249" s="8" t="s">
@@ -14553,7 +14553,7 @@
       <c r="A250" s="8">
         <v>246</v>
       </c>
-      <c r="B250" s="115" t="s">
+      <c r="B250" s="106" t="s">
         <v>557</v>
       </c>
       <c r="C250" s="10" t="s">
@@ -14586,7 +14586,7 @@
       <c r="L250" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M250" s="105" t="b">
+      <c r="M250" s="96" t="b">
         <v>1</v>
       </c>
       <c r="N250" s="8" t="s">
@@ -14631,7 +14631,7 @@
       <c r="L251" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M251" s="107" t="b">
+      <c r="M251" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N251" s="24" t="s">
@@ -14676,7 +14676,7 @@
       <c r="L252" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M252" s="107" t="b">
+      <c r="M252" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N252" s="24" t="s">
@@ -14721,7 +14721,7 @@
       <c r="L253" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M253" s="107" t="b">
+      <c r="M253" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N253" s="24" t="s">
@@ -14766,7 +14766,7 @@
       <c r="L254" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M254" s="107" t="b">
+      <c r="M254" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N254" s="24" t="s">
@@ -14811,7 +14811,7 @@
       <c r="L255" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M255" s="107" t="b">
+      <c r="M255" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N255" s="24" t="s">
@@ -14856,7 +14856,7 @@
       <c r="L256" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M256" s="107" t="b">
+      <c r="M256" s="98" t="b">
         <v>1</v>
       </c>
       <c r="N256" s="24" t="s">
@@ -14895,16 +14895,16 @@
       <c r="J257" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K257" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L257" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M257" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N257" s="130" t="s">
+      <c r="K257" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L257" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M257" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N257" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O257" s="28"/>
@@ -14940,16 +14940,16 @@
       <c r="J258" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K258" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="L258" s="130" t="s">
-        <v>20</v>
-      </c>
-      <c r="M258" s="109" t="b">
-        <v>1</v>
-      </c>
-      <c r="N258" s="130" t="s">
+      <c r="K258" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L258" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M258" s="100" t="b">
+        <v>1</v>
+      </c>
+      <c r="N258" s="121" t="s">
         <v>616</v>
       </c>
       <c r="O258" s="28"/>
@@ -14973,7 +14973,7 @@
       <c r="F259" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="G259" s="124" t="s">
+      <c r="G259" s="115" t="s">
         <v>653</v>
       </c>
       <c r="H259" s="8" t="s">
@@ -14989,7 +14989,7 @@
       <c r="L259" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M259" s="111" t="b">
+      <c r="M259" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N259" s="31" t="s">
@@ -15028,16 +15028,16 @@
       <c r="J260" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K260" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="L260" s="128" t="s">
-        <v>20</v>
-      </c>
-      <c r="M260" s="106" t="b">
-        <v>1</v>
-      </c>
-      <c r="N260" s="129" t="s">
+      <c r="K260" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="L260" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M260" s="97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N260" s="120" t="s">
         <v>616</v>
       </c>
       <c r="O260" s="5"/>
@@ -15079,13 +15079,13 @@
       <c r="L261" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="M261" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="N261" s="99" t="s">
-        <v>616</v>
-      </c>
-      <c r="O261" s="100"/>
+      <c r="M261" s="103" t="b">
+        <v>1</v>
+      </c>
+      <c r="N261" s="90" t="s">
+        <v>616</v>
+      </c>
+      <c r="O261" s="91"/>
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262" s="35">
@@ -15124,13 +15124,13 @@
       <c r="L262" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="M262" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="N262" s="99" t="s">
-        <v>616</v>
-      </c>
-      <c r="O262" s="100"/>
+      <c r="M262" s="103" t="b">
+        <v>1</v>
+      </c>
+      <c r="N262" s="90" t="s">
+        <v>616</v>
+      </c>
+      <c r="O262" s="91"/>
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263" s="31">
@@ -15151,7 +15151,7 @@
       <c r="F263" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G263" s="124" t="s">
+      <c r="G263" s="115" t="s">
         <v>18</v>
       </c>
       <c r="H263" s="8" t="s">
@@ -15169,7 +15169,7 @@
       <c r="L263" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M263" s="111" t="b">
+      <c r="M263" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N263" s="31" t="s">
@@ -15196,7 +15196,7 @@
       <c r="F264" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G264" s="124" t="s">
+      <c r="G264" s="115" t="s">
         <v>132</v>
       </c>
       <c r="H264" s="8" t="s">
@@ -15214,7 +15214,7 @@
       <c r="L264" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M264" s="111" t="b">
+      <c r="M264" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N264" s="31" t="s">
@@ -15241,7 +15241,7 @@
       <c r="F265" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G265" s="124" t="s">
+      <c r="G265" s="115" t="s">
         <v>182</v>
       </c>
       <c r="H265" s="8" t="s">
@@ -15259,7 +15259,7 @@
       <c r="L265" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M265" s="111" t="b">
+      <c r="M265" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N265" s="31" t="s">
@@ -15286,7 +15286,7 @@
       <c r="F266" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G266" s="124" t="s">
+      <c r="G266" s="115" t="s">
         <v>261</v>
       </c>
       <c r="H266" s="8" t="s">
@@ -15304,7 +15304,7 @@
       <c r="L266" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M266" s="111" t="b">
+      <c r="M266" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N266" s="31" t="s">
@@ -15331,7 +15331,7 @@
       <c r="F267" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G267" s="124" t="s">
+      <c r="G267" s="115" t="s">
         <v>323</v>
       </c>
       <c r="H267" s="8" t="s">
@@ -15349,7 +15349,7 @@
       <c r="L267" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M267" s="111" t="b">
+      <c r="M267" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N267" s="31" t="s">
@@ -15376,7 +15376,7 @@
       <c r="F268" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G268" s="124" t="s">
+      <c r="G268" s="115" t="s">
         <v>128</v>
       </c>
       <c r="H268" s="8" t="s">
@@ -15394,7 +15394,7 @@
       <c r="L268" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M268" s="111" t="b">
+      <c r="M268" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N268" s="31" t="s">
@@ -15421,7 +15421,7 @@
       <c r="F269" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G269" s="124" t="s">
+      <c r="G269" s="115" t="s">
         <v>468</v>
       </c>
       <c r="H269" s="8" t="s">
@@ -15439,7 +15439,7 @@
       <c r="L269" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M269" s="111" t="b">
+      <c r="M269" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N269" s="31" t="s">
@@ -15484,13 +15484,13 @@
       <c r="L270" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="M270" s="112" t="b">
-        <v>1</v>
-      </c>
-      <c r="N270" s="99" t="s">
-        <v>616</v>
-      </c>
-      <c r="O270" s="100" t="s">
+      <c r="M270" s="103" t="b">
+        <v>1</v>
+      </c>
+      <c r="N270" s="90" t="s">
+        <v>616</v>
+      </c>
+      <c r="O270" s="91" t="s">
         <v>657</v>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       <c r="F271" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G271" s="124" t="s">
+      <c r="G271" s="115" t="s">
         <v>18</v>
       </c>
       <c r="H271" s="8" t="s">
@@ -15531,7 +15531,7 @@
       <c r="L271" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M271" s="111" t="b">
+      <c r="M271" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N271" s="31" t="s">
@@ -15558,7 +15558,7 @@
       <c r="F272" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G272" s="124" t="s">
+      <c r="G272" s="115" t="s">
         <v>132</v>
       </c>
       <c r="H272" s="8" t="s">
@@ -15576,7 +15576,7 @@
       <c r="L272" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M272" s="111" t="b">
+      <c r="M272" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N272" s="31" t="s">
@@ -15603,7 +15603,7 @@
       <c r="F273" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G273" s="124" t="s">
+      <c r="G273" s="115" t="s">
         <v>182</v>
       </c>
       <c r="H273" s="8" t="s">
@@ -15621,7 +15621,7 @@
       <c r="L273" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M273" s="111" t="b">
+      <c r="M273" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N273" s="31" t="s">
@@ -15648,7 +15648,7 @@
       <c r="F274" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G274" s="124" t="s">
+      <c r="G274" s="115" t="s">
         <v>261</v>
       </c>
       <c r="H274" s="8" t="s">
@@ -15666,7 +15666,7 @@
       <c r="L274" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M274" s="111" t="b">
+      <c r="M274" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N274" s="31" t="s">
@@ -15693,7 +15693,7 @@
       <c r="F275" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G275" s="124" t="s">
+      <c r="G275" s="115" t="s">
         <v>323</v>
       </c>
       <c r="H275" s="8" t="s">
@@ -15711,7 +15711,7 @@
       <c r="L275" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M275" s="111" t="b">
+      <c r="M275" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N275" s="31" t="s">
@@ -15738,7 +15738,7 @@
       <c r="F276" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G276" s="124" t="s">
+      <c r="G276" s="115" t="s">
         <v>128</v>
       </c>
       <c r="H276" s="8" t="s">
@@ -15756,7 +15756,7 @@
       <c r="L276" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M276" s="111" t="b">
+      <c r="M276" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N276" s="31" t="s">
@@ -15783,7 +15783,7 @@
       <c r="F277" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G277" s="124" t="s">
+      <c r="G277" s="115" t="s">
         <v>468</v>
       </c>
       <c r="H277" s="8" t="s">
@@ -15801,7 +15801,7 @@
       <c r="L277" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M277" s="111" t="b">
+      <c r="M277" s="102" t="b">
         <v>1</v>
       </c>
       <c r="N277" s="31" t="s">
@@ -15828,7 +15828,7 @@
       <c r="F278" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="G278" s="124" t="s">
+      <c r="G278" s="115" t="s">
         <v>653</v>
       </c>
       <c r="H278" s="8" t="s">
@@ -15846,7 +15846,7 @@
       <c r="L278" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M278" s="111" t="b">
+      <c r="M278" s="102" t="b">
         <v>0</v>
       </c>
       <c r="N278" s="31" t="s">
@@ -15857,29 +15857,29 @@
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B279" s="125"/>
-      <c r="M279" s="113" t="b">
+      <c r="B279" s="116"/>
+      <c r="M279" s="104" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="1:15" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="79" t="s">
+      <c r="A281" s="126" t="s">
         <v>677</v>
       </c>
-      <c r="B281" s="78"/>
-      <c r="C281" s="78"/>
-      <c r="D281" s="78"/>
-      <c r="E281" s="78"/>
-      <c r="F281" s="78"/>
-      <c r="G281" s="78"/>
-      <c r="H281" s="78"/>
-      <c r="I281" s="78"/>
-      <c r="J281" s="78"/>
-      <c r="K281" s="78"/>
-      <c r="L281" s="78"/>
-      <c r="M281" s="78"/>
-      <c r="N281" s="78"/>
-      <c r="O281" s="78"/>
+      <c r="B281" s="125"/>
+      <c r="C281" s="125"/>
+      <c r="D281" s="125"/>
+      <c r="E281" s="125"/>
+      <c r="F281" s="125"/>
+      <c r="G281" s="125"/>
+      <c r="H281" s="125"/>
+      <c r="I281" s="125"/>
+      <c r="J281" s="125"/>
+      <c r="K281" s="125"/>
+      <c r="L281" s="125"/>
+      <c r="M281" s="125"/>
+      <c r="N281" s="125"/>
+      <c r="O281" s="125"/>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C282" t="s">
@@ -15915,432 +15915,432 @@
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
     <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.7265625" style="104" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.7265625" style="95" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="123" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123" t="s">
+        <v>628</v>
+      </c>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="84" t="s">
+        <v>623</v>
+      </c>
+      <c r="B2" s="85" t="s">
+        <v>624</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>626</v>
+      </c>
+      <c r="D2" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="84" t="s">
+        <v>623</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>624</v>
+      </c>
+      <c r="G2" s="87" t="s">
+        <v>626</v>
+      </c>
+      <c r="H2" s="86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="83">
+        <v>46119</v>
+      </c>
+      <c r="B3" s="117">
+        <v>0.1</v>
+      </c>
+      <c r="C3" s="88" t="s">
+        <v>627</v>
+      </c>
+      <c r="D3" s="93" t="s">
+        <v>625</v>
+      </c>
+      <c r="E3" s="83">
+        <v>46119</v>
+      </c>
+      <c r="F3" s="77">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="88" t="s">
+        <v>627</v>
+      </c>
+      <c r="H3" s="79" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="83">
+        <v>46119</v>
+      </c>
+      <c r="B4" s="117">
+        <v>0.11</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>627</v>
+      </c>
+      <c r="D4" s="93" t="s">
+        <v>647</v>
+      </c>
+      <c r="E4" s="83"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="79"/>
+    </row>
+    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="83">
+        <v>46120</v>
+      </c>
+      <c r="B5" s="117">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="88" t="s">
+        <v>627</v>
+      </c>
+      <c r="D5" s="93" t="s">
+        <v>690</v>
+      </c>
+      <c r="E5" s="78"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="79"/>
+    </row>
+    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="83">
+        <v>46120</v>
+      </c>
+      <c r="B6" s="117">
+        <v>0.8</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>627</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>691</v>
+      </c>
+      <c r="E6" s="78"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="79"/>
+    </row>
+    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="83">
+        <v>46121</v>
+      </c>
+      <c r="B7" s="117">
+        <v>0.9</v>
+      </c>
+      <c r="C7" s="88" t="s">
+        <v>627</v>
+      </c>
+      <c r="D7" s="93" t="s">
         <v>694</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98" t="s">
-        <v>628</v>
-      </c>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="92" t="s">
-        <v>623</v>
-      </c>
-      <c r="B2" s="93" t="s">
-        <v>624</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>626</v>
-      </c>
-      <c r="D2" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="92" t="s">
-        <v>623</v>
-      </c>
-      <c r="F2" s="93" t="s">
-        <v>624</v>
-      </c>
-      <c r="G2" s="95" t="s">
-        <v>626</v>
-      </c>
-      <c r="H2" s="94" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="91">
-        <v>46119</v>
-      </c>
-      <c r="B3" s="126">
-        <v>0.1</v>
-      </c>
-      <c r="C3" s="96" t="s">
-        <v>627</v>
-      </c>
-      <c r="D3" s="102" t="s">
-        <v>625</v>
-      </c>
-      <c r="E3" s="91">
-        <v>46119</v>
-      </c>
-      <c r="F3" s="85">
-        <v>0.1</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>627</v>
-      </c>
-      <c r="H3" s="87" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="91">
-        <v>46119</v>
-      </c>
-      <c r="B4" s="126">
-        <v>0.11</v>
-      </c>
-      <c r="C4" s="96" t="s">
-        <v>627</v>
-      </c>
-      <c r="D4" s="102" t="s">
-        <v>647</v>
-      </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="87"/>
-    </row>
-    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="91">
-        <v>46120</v>
-      </c>
-      <c r="B5" s="126">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="96" t="s">
-        <v>627</v>
-      </c>
-      <c r="D5" s="102" t="s">
-        <v>691</v>
-      </c>
-      <c r="E5" s="86"/>
-      <c r="F5" s="85"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="87"/>
-    </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="91">
-        <v>46120</v>
-      </c>
-      <c r="B6" s="126">
-        <v>0.8</v>
-      </c>
-      <c r="C6" s="96" t="s">
-        <v>627</v>
-      </c>
-      <c r="D6" s="102" t="s">
+      <c r="E7" s="78"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="79"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="78"/>
+      <c r="B8" s="117">
+        <v>1</v>
+      </c>
+      <c r="C8" s="88"/>
+      <c r="D8" s="93" t="s">
         <v>692</v>
       </c>
-      <c r="E6" s="86"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="87"/>
-    </row>
-    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="91">
-        <v>46121</v>
-      </c>
-      <c r="B7" s="126">
-        <v>0.9</v>
-      </c>
-      <c r="C7" s="96" t="s">
-        <v>627</v>
-      </c>
-      <c r="D7" s="102" t="s">
-        <v>695</v>
-      </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="87"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
-      <c r="B8" s="126">
-        <v>1</v>
-      </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="102" t="s">
-        <v>693</v>
-      </c>
-      <c r="E8" s="86"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="87"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="79"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="86"/>
-      <c r="B9" s="126"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="87"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="79"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="86"/>
-      <c r="B10" s="126"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="87"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="79"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="86"/>
-      <c r="B11" s="126"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="87"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="79"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="86"/>
-      <c r="B12" s="126"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="87"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="79"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="86"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="87"/>
+      <c r="A13" s="78"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="79"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="86"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="87"/>
+      <c r="A14" s="78"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="93"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="86"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="87"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="79"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="86"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="87"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="88"/>
+      <c r="H16" s="79"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="86"/>
-      <c r="B17" s="126"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="96"/>
-      <c r="H17" s="87"/>
+      <c r="A17" s="78"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="79"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="86"/>
-      <c r="B18" s="126"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="87"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="117"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="79"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="86"/>
-      <c r="B19" s="126"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="87"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="79"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="86"/>
-      <c r="B20" s="126"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="87"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="79"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="86"/>
-      <c r="B21" s="126"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="87"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="79"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="86"/>
-      <c r="B22" s="126"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="102"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="96"/>
-      <c r="H22" s="87"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="79"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="86"/>
-      <c r="B23" s="126"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="87"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="79"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="86"/>
-      <c r="B24" s="126"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="87"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="79"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="86"/>
-      <c r="B25" s="126"/>
-      <c r="C25" s="96"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="87"/>
+      <c r="A25" s="78"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="79"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="86"/>
-      <c r="B26" s="126"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="87"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="79"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="86"/>
-      <c r="B27" s="126"/>
-      <c r="C27" s="96"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="96"/>
-      <c r="H27" s="87"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="79"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="86"/>
-      <c r="B28" s="126"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="96"/>
-      <c r="H28" s="87"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="117"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="79"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="86"/>
-      <c r="B29" s="126"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="96"/>
-      <c r="H29" s="87"/>
+      <c r="A29" s="78"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="79"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="86"/>
-      <c r="B30" s="126"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="87"/>
+      <c r="A30" s="78"/>
+      <c r="B30" s="117"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="79"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="86"/>
-      <c r="B31" s="126"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="87"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="78"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="79"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="86"/>
-      <c r="B32" s="126"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="87"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="117"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="79"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="86"/>
-      <c r="B33" s="126"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="87"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="88"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="78"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="79"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="86"/>
-      <c r="B34" s="126"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="96"/>
-      <c r="H34" s="87"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="117"/>
+      <c r="C34" s="88"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="79"/>
     </row>
     <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="88"/>
-      <c r="B35" s="127"/>
-      <c r="C35" s="97"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="90"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="118"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16366,12 +16366,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="129" t="s">
         <v>584</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
     </row>
     <row r="2" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -16512,56 +16512,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="130" t="s">
         <v>618</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="127" t="s">
         <v>629</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
     </row>
     <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+      <c r="F3" s="125"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -21527,21 +21527,21 @@
       <c r="M262" s="72"/>
     </row>
     <row r="264" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="84" t="s">
+      <c r="A264" s="131" t="s">
         <v>619</v>
       </c>
-      <c r="B264" s="78"/>
-      <c r="C264" s="78"/>
-      <c r="D264" s="78"/>
-      <c r="E264" s="78"/>
-      <c r="F264" s="78"/>
-      <c r="G264" s="78"/>
-      <c r="H264" s="78"/>
-      <c r="I264" s="78"/>
-      <c r="J264" s="78"/>
-      <c r="K264" s="78"/>
-      <c r="L264" s="78"/>
-      <c r="M264" s="78"/>
+      <c r="B264" s="125"/>
+      <c r="C264" s="125"/>
+      <c r="D264" s="125"/>
+      <c r="E264" s="125"/>
+      <c r="F264" s="125"/>
+      <c r="G264" s="125"/>
+      <c r="H264" s="125"/>
+      <c r="I264" s="125"/>
+      <c r="J264" s="125"/>
+      <c r="K264" s="125"/>
+      <c r="L264" s="125"/>
+      <c r="M264" s="125"/>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="C265" t="s">
